--- a/CORE/Localization/LocalizationTable.xlsx
+++ b/CORE/Localization/LocalizationTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\___MYPROJECT___\UnityProject\MFramework\ExcelData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D3001E-ECA3-42B5-8761-0B723213BC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381943F3-4BCE-4658-A20C-2F169AADCD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="19470" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>编号</t>
   </si>
@@ -64,137 +64,55 @@
     <t>1</t>
   </si>
   <si>
-    <t>StartText</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>OptionsText</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>ExitText</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>LanguageText</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>SoundText</t>
-  </si>
-  <si>
     <t>开始</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Start</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Settings</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>退出</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语言:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中文</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Language:English</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>音量:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>{#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>关</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound:{#On|Off}</t>
+    <t>START</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平台游戏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Platform Game</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>存档选择</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>File Select</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加载</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新游戏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Game</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -202,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -229,23 +147,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -267,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -279,9 +180,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -618,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -683,76 +581,111 @@
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>32</v>
-      </c>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/CORE/Localization/LocalizationTable.xlsx
+++ b/CORE/Localization/LocalizationTable.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\___UnityProject___\MFramework\CORE\Localization\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAAC2F5-758E-4B4E-A897-F8AABB411932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -85,12 +92,24 @@
     <t>MText(Multi)</t>
   </si>
   <si>
+    <t>按下任意键开始</t>
+  </si>
+  <si>
+    <t>PRESS ANY BUTTON</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>Title(Multi)</t>
   </si>
   <si>
+    <t>平台游戏</t>
+  </si>
+  <si>
+    <t>Platform Game</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -100,21 +119,45 @@
     <t>FileSelectTitle(Multi)</t>
   </si>
   <si>
+    <t>存档选择</t>
+  </si>
+  <si>
+    <t>File Select</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>SaveCardWidget</t>
   </si>
   <si>
+    <t>加载</t>
+  </si>
+  <si>
+    <t>LOAD</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
+    <t>新游戏</t>
+  </si>
+  <si>
+    <t>New Game</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
     <t>EmptyTitle(Multi)</t>
   </si>
   <si>
+    <t>空存档</t>
+  </si>
+  <si>
+    <t>EMPTY</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -124,6 +167,12 @@
     <t>LevelSelectTitle(Multi)</t>
   </si>
   <si>
+    <t>关卡选择</t>
+  </si>
+  <si>
+    <t>Level Select</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -133,115 +182,79 @@
     <t>PauseText(Multi)</t>
   </si>
   <si>
+    <t>暂停</t>
+  </si>
+  <si>
+    <t>PAUSED</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
+    <t>继续</t>
+  </si>
+  <si>
+    <t>RESUME</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
+    <t>从上一个存档点开始</t>
+  </si>
+  <si>
+    <t>RESUME FROM LAST CHECKPOINT</t>
+  </si>
+  <si>
     <t>11</t>
   </si>
   <si>
+    <t>重置</t>
+  </si>
+  <si>
+    <t>RESTART</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>EXIT</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
     <t>LoadingPanel</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>LevelCardWidget</t>
-  </si>
-  <si>
-    <t>开始</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-  <si>
-    <t>平台游戏</t>
-  </si>
-  <si>
-    <t>Platform Game</t>
-  </si>
-  <si>
-    <t>存档选择</t>
-  </si>
-  <si>
-    <t>File Select</t>
-  </si>
-  <si>
-    <t>加载</t>
-  </si>
-  <si>
-    <t>LOAD</t>
-  </si>
-  <si>
-    <t>新游戏</t>
-  </si>
-  <si>
-    <t>New Game</t>
-  </si>
-  <si>
-    <t>空存档</t>
-  </si>
-  <si>
-    <t>EMPTY</t>
-  </si>
-  <si>
-    <t>关卡选择</t>
-  </si>
-  <si>
-    <t>Level Select</t>
-  </si>
-  <si>
-    <t>暂停</t>
-  </si>
-  <si>
-    <t>PAUSED</t>
-  </si>
-  <si>
-    <t>继续</t>
-  </si>
-  <si>
-    <t>RESUME</t>
-  </si>
-  <si>
-    <t>从上一个存档点开始</t>
-  </si>
-  <si>
-    <t>RESUME FROM LAST CHECKPOINT</t>
-  </si>
-  <si>
-    <t>重置</t>
-  </si>
-  <si>
-    <t>RESTART</t>
-  </si>
-  <si>
-    <t>退出</t>
-  </si>
-  <si>
-    <t>EXIT</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>加载中</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>...</t>
     </r>
   </si>
   <si>
     <t>Loading...</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>LevelCardWidget</t>
   </si>
   <si>
     <t>游玩</t>
@@ -253,39 +266,377 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -293,33 +644,319 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -368,7 +1005,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -401,26 +1038,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -453,23 +1073,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -631,394 +1234,389 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="40.5546875" customWidth="1"/>
+    <col min="1" max="1" width="9.10833333333333" customWidth="1"/>
+    <col min="2" max="2" width="40.5583333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" customWidth="1"/>
+    <col min="4" max="4" width="19.1083333333333" customWidth="1"/>
+    <col min="5" max="5" width="9.10833333333333" customWidth="1"/>
+    <col min="6" max="6" width="24.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="33.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="15" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="15" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="15" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="G10" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>48</v>
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>50</v>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>52</v>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>54</v>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="15" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>58</v>
+      <c r="C16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="2" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/CORE/Localization/LocalizationTable.xlsx
+++ b/CORE/Localization/LocalizationTable.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\___UnityProject___\MFramework\CORE\Localization\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA30FBA3-3988-44B9-8BA6-02F10591B865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <si>
     <t>编号</t>
   </si>
@@ -242,7 +248,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>...</t>
     </r>
@@ -261,19 +267,21 @@
   </si>
   <si>
     <t>PLAY</t>
+  </si>
+  <si>
+    <t>设置</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Settings</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -283,7 +291,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -292,351 +300,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -644,253 +331,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -901,62 +346,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1234,25 +639,25 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.10833333333333" customWidth="1"/>
-    <col min="2" max="2" width="40.5583333333333" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="40.5546875" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="19.1083333333333" customWidth="1"/>
-    <col min="5" max="5" width="9.10833333333333" customWidth="1"/>
-    <col min="6" max="6" width="24.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="33.4416666666667" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1298,7 +703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1321,7 +726,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1342,7 +747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1363,7 +768,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1384,7 +789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1405,7 +810,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1426,7 +831,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1447,7 +852,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1468,7 +873,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>48</v>
       </c>
@@ -1489,7 +894,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -1510,7 +915,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>56</v>
       </c>
@@ -1531,7 +936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>59</v>
       </c>
@@ -1552,7 +957,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>62</v>
       </c>
@@ -1573,7 +978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>65</v>
       </c>
@@ -1594,7 +999,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>69</v>
       </c>
@@ -1615,8 +1020,19 @@
         <v>72</v>
       </c>
     </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/CORE/Localization/LocalizationTable.xlsx
+++ b/CORE/Localization/LocalizationTable.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\___UnityProject___\MFramework\CORE\Localization\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA30FBA3-3988-44B9-8BA6-02F10591B865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
   <si>
     <t>编号</t>
   </si>
@@ -89,81 +83,84 @@
     <t>1</t>
   </si>
   <si>
-    <t>3DGame_TitleScreen|3DGame_SampleLevel</t>
+    <t>3DGame_TitleScreen|3DGame_SampleLevel|3DGame_Level1</t>
   </si>
   <si>
     <t>TitleScreenPanel</t>
   </si>
   <si>
+    <t>HintText(Multi)</t>
+  </si>
+  <si>
+    <t>PRESS ANY BUTTON</t>
+  </si>
+  <si>
+    <t>按下任意键开始</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Title(Multi)</t>
+  </si>
+  <si>
+    <t>Platform Game</t>
+  </si>
+  <si>
+    <t>平台游戏</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>FileSelectPanel</t>
+  </si>
+  <si>
+    <t>FileSelectTitle(Multi)</t>
+  </si>
+  <si>
+    <t>File Select</t>
+  </si>
+  <si>
+    <t>存档选择</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>SaveCardWidget</t>
+  </si>
+  <si>
     <t>MText(Multi)</t>
   </si>
   <si>
-    <t>按下任意键开始</t>
-  </si>
-  <si>
-    <t>PRESS ANY BUTTON</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Title(Multi)</t>
-  </si>
-  <si>
-    <t>平台游戏</t>
-  </si>
-  <si>
-    <t>Platform Game</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>FileSelectPanel</t>
-  </si>
-  <si>
-    <t>FileSelectTitle(Multi)</t>
-  </si>
-  <si>
-    <t>存档选择</t>
-  </si>
-  <si>
-    <t>File Select</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>SaveCardWidget</t>
+    <t>LOAD</t>
   </si>
   <si>
     <t>加载</t>
   </si>
   <si>
-    <t>LOAD</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
+    <t>New Game</t>
+  </si>
+  <si>
     <t>新游戏</t>
   </si>
   <si>
-    <t>New Game</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
     <t>EmptyTitle(Multi)</t>
   </si>
   <si>
+    <t>EMPTY</t>
+  </si>
+  <si>
     <t>空存档</t>
   </si>
   <si>
-    <t>EMPTY</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -173,12 +170,12 @@
     <t>LevelSelectTitle(Multi)</t>
   </si>
   <si>
+    <t>Level Select</t>
+  </si>
+  <si>
     <t>关卡选择</t>
   </si>
   <si>
-    <t>Level Select</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -188,52 +185,55 @@
     <t>PauseText(Multi)</t>
   </si>
   <si>
+    <t>PAUSED</t>
+  </si>
+  <si>
     <t>暂停</t>
   </si>
   <si>
-    <t>PAUSED</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
+    <t>RESUME</t>
+  </si>
+  <si>
     <t>继续</t>
   </si>
   <si>
-    <t>RESUME</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
+    <t>RESUME FROM LAST CHECKPOINT</t>
+  </si>
+  <si>
     <t>从上一个存档点开始</t>
   </si>
   <si>
-    <t>RESUME FROM LAST CHECKPOINT</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
+    <t>RESTART</t>
+  </si>
+  <si>
     <t>重置</t>
   </si>
   <si>
-    <t>RESTART</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
+    <t>EXIT</t>
+  </si>
+  <si>
     <t>退出</t>
   </si>
   <si>
-    <t>EXIT</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
     <t>LoadingPanel</t>
+  </si>
+  <si>
+    <t>Loading...</t>
   </si>
   <si>
     <r>
@@ -248,40 +248,68 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>...</t>
     </r>
   </si>
   <si>
-    <t>Loading...</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
     <t>LevelCardWidget</t>
   </si>
   <si>
+    <t>PLAY</t>
+  </si>
+  <si>
     <t>游玩</t>
   </si>
   <si>
-    <t>PLAY</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>SettingWidget</t>
+  </si>
+  <si>
+    <t>Settings</t>
   </si>
   <si>
     <t>设置</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Settings</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Text(Multi)</t>
+  </si>
+  <si>
+    <t>SFX</t>
+  </si>
+  <si>
+    <t>效果音</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>背景音乐</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -291,7 +319,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -300,30 +328,351 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -331,44 +680,549 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -378,44 +1232,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -445,12 +1299,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -539,6 +1393,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -547,13 +1408,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -618,46 +1472,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="40.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.14166666666667" customWidth="1"/>
+    <col min="2" max="2" width="51.95" customWidth="1"/>
+    <col min="3" max="3" width="14.825" customWidth="1"/>
+    <col min="4" max="4" width="18.725" customWidth="1"/>
+    <col min="5" max="5" width="34.125" customWidth="1"/>
+    <col min="6" max="6" width="28.625" customWidth="1"/>
+    <col min="7" max="7" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" ht="15" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,7 +1514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" ht="15" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -703,7 +1537,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" ht="15" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -726,7 +1560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -739,15 +1573,17 @@
       <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -760,15 +1596,17 @@
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -781,15 +1619,17 @@
       <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -800,19 +1640,21 @@
         <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -821,19 +1663,21 @@
         <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
@@ -842,197 +1686,273 @@
         <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="F11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="F12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="F13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="F15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="F16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>15</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>73</v>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/CORE/Localization/LocalizationTable.xlsx
+++ b/CORE/Localization/LocalizationTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="93">
   <si>
     <t>编号</t>
   </si>
@@ -297,6 +297,107 @@
   </si>
   <si>
     <t>背景音乐</t>
+  </si>
+  <si>
+    <t>对话板</t>
+  </si>
+  <si>
+    <t>踩下所有柱子</t>
+  </si>
+  <si>
+    <t>Stamp all Logs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>史莱姆对话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>左前方有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;exclaim(1,1.1,255,0,0)&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>隐藏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>~</t>
+    </r>
+  </si>
+  <si>
+    <t>There's a &lt;exclaim(1,1.1,255,0,0)&gt;hiding&lt;/&gt; on the left front~</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>史莱姆对话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>GOGOGOGOGO~~~~~~~~</t>
   </si>
 </sst>
 </file>
@@ -926,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -945,6 +1046,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1479,7 +1592,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.14166666666667" customWidth="1"/>
@@ -1487,8 +1600,8 @@
     <col min="3" max="3" width="14.825" customWidth="1"/>
     <col min="4" max="4" width="18.725" customWidth="1"/>
     <col min="5" max="5" width="34.125" customWidth="1"/>
-    <col min="6" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="34.875" customWidth="1"/>
+    <col min="6" max="6" width="40.875" customWidth="1"/>
+    <col min="7" max="7" width="52.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:7">
@@ -1951,6 +2064,57 @@
         <v>83</v>
       </c>
     </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="7">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="9">
+        <v>100</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="9">
+        <v>101</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
